--- a/data/output/2025/evaluasi_21.xlsx
+++ b/data/output/2025/evaluasi_21.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2171" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2172" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2102" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2101" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1737,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1798,342 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.07518221962861084</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.005625947603314109</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.13007436025027</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.376050881399434</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.411905913475029</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.0453874772878058</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1424336002578235</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.236420898175841</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.240206538941132</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.880848928624167</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.192266325562939</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1811,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,6 +2516,454 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.132913546228284</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.07974443528900779</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>25.08461130681152</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-8.663057281186067</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.711876984898388</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5176737511899761</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6692863223704759</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.359693758367301</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.748045869318165</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5.030197241389041</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9.906040454230123</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6.897848709750258</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6.246958669241105</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.794495498660467</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-2.1236562052957</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,6 +3066,258 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>23.9479554725869</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-7.304385317628586</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.2090611433058</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.008388722033050541</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2856235490562792</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.724537906405342</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.960287862308414</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.266200052194682</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2295,7 +3332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +3392,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.9440000000000029</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>27.80453349544982</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-9.072648688350297</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.726046183941078</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.088169688648621</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.008549330855685159</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.4200000000000454</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.649412405118425</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.468639107184382</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Batam</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.264586335091984</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2369,7 +3714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2485,6 +3830,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.8367206615869267</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>32.98466316854001</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.547548337965591</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3558481436625434</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.09907741064750138</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.073983993891661</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.993880703164207</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.42804254569587</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2499,7 +4096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,6 +4215,528 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.384075975412492</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.86541053434854</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.932018980881816</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08151909749414264</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bintan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.474039078182615</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.1386882595320291</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.628043068214585</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25.04006802531661</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-7.054477150881468</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.277670121519269</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8209188946498047</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.8980876224712633</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.292483902580016</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.593166327680098</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.420198770053441</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
